--- a/frontend/public/catalogs/ONGC_Material_Catalog_2026.xlsx
+++ b/frontend/public/catalogs/ONGC_Material_Catalog_2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Material Catalog" sheetId="1" r:id="rId1"/>
+    <sheet name="ONGC_Materials" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -421,70 +421,70 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ONGC-PIP-CS-1001</v>
+        <v>ONGC-INST-DPT-250M</v>
       </c>
       <c r="B2" t="str">
-        <v>Pipe Seamless Carbon Steel ASTM A106 Gr B 6" Sch 40 Beveled End</v>
+        <v>Differential Pressure Transmitter Range 0-250 mbar Output 4-20mA HART Diaphragm Hastelloy C-276 Flanged Process Connection</v>
       </c>
       <c r="C2" t="str">
-        <v>Pipes</v>
+        <v>Instrumentation</v>
       </c>
       <c r="D2" t="str">
-        <v>Mtr</v>
+        <v>Nos</v>
       </c>
       <c r="E2">
-        <v>4850</v>
+        <v>78500</v>
       </c>
       <c r="F2">
-        <v>12000</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ONGC-PIP-CS-1002</v>
+        <v>ONGC-VLV-BF-08-150</v>
       </c>
       <c r="B3" t="str">
-        <v>Pipe Seamless Carbon Steel ASTM A106 Gr B 4" Sch 40 Beveled End</v>
+        <v>Triple Offset Butterfly Valve 8" Class 150 Lug Type Body ASTM A216 WCB Disc SS316 Metal Seated API 609 Gear Operated</v>
       </c>
       <c r="C3" t="str">
-        <v>Pipes</v>
+        <v>Valves</v>
       </c>
       <c r="D3" t="str">
-        <v>Mtr</v>
+        <v>Nos</v>
       </c>
       <c r="E3">
-        <v>3200</v>
+        <v>64000</v>
       </c>
       <c r="F3">
-        <v>8500</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ONGC-PIP-SS-2001</v>
+        <v>ONGC-INST-CMF-02-300</v>
       </c>
       <c r="B4" t="str">
-        <v>Pipe Stainless Steel Seamless ASTM A312 TP316L 2" Sch 40S</v>
+        <v>Coriolis Mass Flow Meter 2" Class 300 Flanged SS316L Flow Tube 0-50000 kg/hr with Integral Transmitter 4-20mA HART</v>
       </c>
       <c r="C4" t="str">
-        <v>Pipes</v>
+        <v>Instrumentation</v>
       </c>
       <c r="D4" t="str">
-        <v>Mtr</v>
+        <v>Nos</v>
       </c>
       <c r="E4">
-        <v>8900</v>
+        <v>320000</v>
       </c>
       <c r="F4">
-        <v>4500</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ONGC-PIP-API-3001</v>
+        <v>ONGC-PIP-LTCS-8080</v>
       </c>
       <c r="B5" t="str">
-        <v>Line Pipe Seamless API 5L Gr X52 PSL2 8" Sch 40 3LPE Coated</v>
+        <v>Pipe Seamless LTCS Low Temp Carbon Steel ASTM A333 Grade 6 8" Sch 80 Beveled Ends</v>
       </c>
       <c r="C5" t="str">
         <v>Pipes</v>
@@ -493,38 +493,38 @@
         <v>Mtr</v>
       </c>
       <c r="E5">
-        <v>11500</v>
+        <v>14200</v>
       </c>
       <c r="F5">
-        <v>15000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ONGC-VLV-BL-3004</v>
+        <v>ONGC-INST-RTD-400D</v>
       </c>
       <c r="B6" t="str">
-        <v>Ball Valve 4" Class 300 Flanged Full Bore ASTM A216 WCB Lever Operated API 6D</v>
+        <v>Duplex Pt100 RTD Temperature Sensor 3-Wire Class A with Flanged Thermowell 1-1/2" 300# Insertion Length 400mm SS316</v>
       </c>
       <c r="C6" t="str">
-        <v>Valves</v>
+        <v>Instrumentation</v>
       </c>
       <c r="D6" t="str">
         <v>Nos</v>
       </c>
       <c r="E6">
-        <v>24500</v>
+        <v>12500</v>
       </c>
       <c r="F6">
-        <v>450</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ONGC-VLV-GT-1506</v>
+        <v>ONGC-VLV-NDL-12-6K</v>
       </c>
       <c r="B7" t="str">
-        <v>Gate Valve 6" Class 150 Flanged Bolted Bonnet ASTM A216 WCB Trim 8 API 600</v>
+        <v>Needle Valve 1/2" NPT Female x Female Rating 6000 PSI Stainless Steel SS316 Body &amp; Stem PTFE Packing</v>
       </c>
       <c r="C7" t="str">
         <v>Valves</v>
@@ -533,278 +533,278 @@
         <v>Nos</v>
       </c>
       <c r="E7">
-        <v>38000</v>
+        <v>4200</v>
       </c>
       <c r="F7">
-        <v>320</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ONGC-VLV-CK-3003</v>
+        <v>ONGC-FLG-SPB-08-300</v>
       </c>
       <c r="B8" t="str">
-        <v>Swing Check Valve 3" Class 300 Flanged ASTM A216 WCB API 6D Trim 5</v>
+        <v>Spectacle Blind 8" Class 300 Raised Face ASME B16.48 Carbon Steel ASTM A516 Gr 70 Smooth Finish</v>
       </c>
       <c r="C8" t="str">
-        <v>Valves</v>
+        <v>Fittings</v>
       </c>
       <c r="D8" t="str">
         <v>Nos</v>
       </c>
       <c r="E8">
-        <v>16500</v>
+        <v>8400</v>
       </c>
       <c r="F8">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ONGC-VLV-GL-3002</v>
+        <v>ONGC-GSK-RTJ-R45-SI</v>
       </c>
       <c r="B9" t="str">
-        <v>Globe Valve 2" Class 300 Flanged OS&amp;Y Rising Stem ASTM A216 WCB BS 1873</v>
+        <v>Metallic Ring Joint Gasket RTJ R-45 Octagonal Cross Section Soft Iron Max Hardness 90 HB ASME B16.20</v>
       </c>
       <c r="C9" t="str">
-        <v>Valves</v>
+        <v>Fittings</v>
       </c>
       <c r="D9" t="str">
         <v>Nos</v>
       </c>
       <c r="E9">
-        <v>14200</v>
+        <v>1850</v>
       </c>
       <c r="F9">
-        <v>350</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ONGC-FAS-ST-B712</v>
+        <v>ONGC-ELEC-FLD-200W</v>
       </c>
       <c r="B10" t="str">
-        <v>Stud Bolt M20 x 120mm ASTM A193 Gr B7 with 2 Heavy Hex Nuts ASTM A194 Gr 2H</v>
+        <v>Explosion Proof High Mast LED Floodlight 200W Ex d IIC T5 Gb IP66 230V AC Flameproof Cast Aluminium Alloy Body</v>
       </c>
       <c r="C10" t="str">
-        <v>Fasteners</v>
+        <v>Electrical</v>
       </c>
       <c r="D10" t="str">
-        <v>Set</v>
+        <v>Nos</v>
       </c>
       <c r="E10">
-        <v>340</v>
+        <v>34500</v>
       </c>
       <c r="F10">
-        <v>25000</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ONGC-FAS-ST-B716</v>
+        <v>ONGC-SAF-GAS-4DET</v>
       </c>
       <c r="B11" t="str">
-        <v>Stud Bolt M24 x 160mm ASTM A193 Gr B7 with 2 Heavy Hex Nuts ASTM A194 Gr 2H</v>
+        <v>Portable Multi-Gas Detector 4-Gas (LEL, O2, H2S, CO) with Internal Sampling Pump Li-Ion Rechargeable Battery ATEX / IECEx Certified</v>
       </c>
       <c r="C11" t="str">
-        <v>Fasteners</v>
+        <v>Safety</v>
       </c>
       <c r="D11" t="str">
-        <v>Set</v>
+        <v>Nos</v>
       </c>
       <c r="E11">
-        <v>520</v>
+        <v>56000</v>
       </c>
       <c r="F11">
-        <v>18000</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ONGC-FAS-ST-B8M</v>
+        <v>ONGC-SAF-SCBA-68L</v>
       </c>
       <c r="B12" t="str">
-        <v>Stud Bolt M16 x 90mm Stainless Steel ASTM A193 Gr B8M with 2 Nuts A194 Gr 8M</v>
+        <v>Self-Contained Breathing Apparatus SCBA 300 Bar 6.8 Litre Carbon Composite Cylinder Full Face Mask Demand Valve EN 137 Type 2</v>
       </c>
       <c r="C12" t="str">
-        <v>Fasteners</v>
+        <v>Safety</v>
       </c>
       <c r="D12" t="str">
         <v>Set</v>
       </c>
       <c r="E12">
-        <v>780</v>
+        <v>82000</v>
       </c>
       <c r="F12">
-        <v>9500</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ONGC-FLG-WN-3006</v>
+        <v>ONGC-VLV-CK-06-300D</v>
       </c>
       <c r="B13" t="str">
-        <v>Weld Neck Flange 6" Class 300 Raised Face ASME B16.5 ASTM A105 Sch 40 Bore</v>
+        <v>Dual Plate Check Valve 6" Class 300 Wafer Type Body &amp; Plates Duplex Stainless Steel UNS S31803 Inconel X-750 Spring API 594</v>
       </c>
       <c r="C13" t="str">
-        <v>Fittings</v>
+        <v>Valves</v>
       </c>
       <c r="D13" t="str">
         <v>Nos</v>
       </c>
       <c r="E13">
-        <v>6200</v>
+        <v>52000</v>
       </c>
       <c r="F13">
-        <v>1200</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ONGC-FLG-WN-1504</v>
+        <v>ONGC-TUB-AST-508-45</v>
       </c>
       <c r="B14" t="str">
-        <v>Weld Neck Flange 4" Class 150 Raised Face ASME B16.5 ASTM A105 Sch 40 Bore</v>
+        <v>Seamless Alloy Steel Tube ASTM A213 Grade T22 Outside Diameter 50.8mm Wall Thickness 4.5mm Cold Drawn</v>
       </c>
       <c r="C14" t="str">
-        <v>Fittings</v>
+        <v>Pipes</v>
       </c>
       <c r="D14" t="str">
-        <v>Nos</v>
+        <v>Mtr</v>
       </c>
       <c r="E14">
-        <v>3400</v>
+        <v>3850</v>
       </c>
       <c r="F14">
-        <v>1600</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ONGC-FIT-ELB-906</v>
+        <v>ONGC-MEC-BRG-6312</v>
       </c>
       <c r="B15" t="str">
-        <v>90 Deg Long Radius Elbow 6" Sch 40 Carbon Steel ASTM A234 Gr WPB ASME B16.9</v>
+        <v>Deep Groove Ball Bearing 6312-2Z Shielded Both Sides Bore 60mm OD 130mm Width 31mm C3 Clearance SKF / FAG</v>
       </c>
       <c r="C15" t="str">
-        <v>Fittings</v>
+        <v>Mechanical</v>
       </c>
       <c r="D15" t="str">
         <v>Nos</v>
       </c>
       <c r="E15">
-        <v>2800</v>
+        <v>3100</v>
       </c>
       <c r="F15">
-        <v>2200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ONGC-GSK-SW-3006</v>
+        <v>ONGC-DRL-MUD-MTR-700</v>
       </c>
       <c r="B16" t="str">
-        <v>Spiral Wound Gasket 6" Class 300 SS316 with Flexible Graphite Filler ASME B16.20</v>
+        <v>Positive Displacement Downhole Mud Motor 7" OD 5/6 Lobe for Directional Drilling API 7-1</v>
       </c>
       <c r="C16" t="str">
-        <v>Fittings</v>
+        <v>Drilling</v>
       </c>
       <c r="D16" t="str">
         <v>Nos</v>
       </c>
       <c r="E16">
-        <v>450</v>
+        <v>940000</v>
       </c>
       <c r="F16">
-        <v>14000</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ONGC-MECH-SEAL-01</v>
+        <v>ONGC-OFF-MOOR-CHN-76</v>
       </c>
       <c r="B17" t="str">
-        <v>Cartridge Mechanical Seal 50mm Shaft Single Spring for Crude Oil Service API 682</v>
+        <v>Stud Link Anchor Mooring Chain Grade R4 76mm Dia Offshore Quality Certified</v>
       </c>
       <c r="C17" t="str">
-        <v>Mechanical</v>
+        <v>Offshore</v>
       </c>
       <c r="D17" t="str">
-        <v>Nos</v>
+        <v>Mtr</v>
       </c>
       <c r="E17">
-        <v>42000</v>
+        <v>18200</v>
       </c>
       <c r="F17">
-        <v>110</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ONGC-ELEC-LED-60W</v>
+        <v>ONGC-SUB-XMAS-TR-10K</v>
       </c>
       <c r="B18" t="str">
-        <v>Flameproof Wellhead LED Well Light 60W Ex d IIC T6 IP66 230V AC</v>
+        <v>Subsea Dual Bore Wellhead Tree Valve Trim 10000 PSI Inconel 718 Lined</v>
       </c>
       <c r="C18" t="str">
-        <v>Electrical</v>
+        <v>Wellhead</v>
       </c>
       <c r="D18" t="str">
         <v>Nos</v>
       </c>
       <c r="E18">
-        <v>18500</v>
+        <v>1450000</v>
       </c>
       <c r="F18">
-        <v>850</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ONGC-SAF-HLM-WHT</v>
+        <v>ONGC-SEP-CYC-DES-01</v>
       </c>
       <c r="B19" t="str">
-        <v>Safety Helmet Industrial Grade HDPE Ratchet Type White Colour IS 2925</v>
+        <v>Hydrocyclone Desander Liner Polyurethane 2 Inch for Offshore Produced Water</v>
       </c>
       <c r="C19" t="str">
-        <v>Safety</v>
+        <v>Mechanical</v>
       </c>
       <c r="D19" t="str">
         <v>Nos</v>
       </c>
       <c r="E19">
-        <v>480</v>
+        <v>28500</v>
       </c>
       <c r="F19">
-        <v>6000</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ONGC-SAF-GLV-NIT</v>
+        <v>ONGC-RIG-ELEC-VFD-1K</v>
       </c>
       <c r="B20" t="str">
-        <v>Heavy Duty Nitrile Chemical Resistant Gloves 13 Inch Gauntlet EN 388</v>
+        <v>Rig Drive Drilling VFD Inverter Module 690V 1200A Liquid Cooled</v>
       </c>
       <c r="C20" t="str">
-        <v>Safety</v>
+        <v>Electrical</v>
       </c>
       <c r="D20" t="str">
-        <v>Pair</v>
+        <v>Nos</v>
       </c>
       <c r="E20">
-        <v>320</v>
+        <v>580000</v>
       </c>
       <c r="F20">
-        <v>12000</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ONGC-DRL-BIT-850</v>
+        <v>ONGC-DRL-STB-1225</v>
       </c>
       <c r="B21" t="str">
-        <v>PDC Drilling Bit 8-1/2 Inch 5-Blade Matrix Body 16mm Cutters API Spec 7-1</v>
+        <v>Near Bit Integral Blade Drilling Stabilizer 12-1/4" AISI 4145H Hardfaced</v>
       </c>
       <c r="C21" t="str">
         <v>Drilling</v>
@@ -813,10 +813,10 @@
         <v>Nos</v>
       </c>
       <c r="E21">
-        <v>385000</v>
+        <v>215000</v>
       </c>
       <c r="F21">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
